--- a/assets/docs/relatorios/comunicacao-que-aproxima-2026-05/participantes.xlsx
+++ b/assets/docs/relatorios/comunicacao-que-aproxima-2026-05/participantes.xlsx
@@ -35,12 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -437,19 +433,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Makerly Aparecida Maia Toledo</v>
+        <v>Adriana Cristiene Demétrio</v>
       </c>
       <c r="B2" t="str">
-        <v>makerlymaiatoledo@gmail.com</v>
+        <v>adriana.demetrio@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C2" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D2" t="str">
-        <v>Diretor</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E2" t="str">
-        <v>3499-5</v>
+        <v>9257</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -458,7 +454,7 @@
         <v>Sim</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-19 15:46:12</v>
+        <v>2026-05-20 09:24:52</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -466,19 +462,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Renata dos Santos Nestor</v>
+        <v>Adriane Marques</v>
       </c>
       <c r="B3" t="str">
-        <v>renata.nestor@pedroleopoldo.mg.gov.br</v>
+        <v>adrianemarquezcursos@gmail.com</v>
       </c>
       <c r="C3" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D3" t="str">
-        <v>DCA 3</v>
+        <v>Assesoria e Atendimento</v>
       </c>
       <c r="E3" t="str">
-        <v>08307</v>
+        <v>35078</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -487,7 +483,7 @@
         <v>Sim</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-05-19 15:47:55</v>
+        <v>2026-05-20 09:10:05</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -495,19 +491,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>João Pedro Corrêa Peixoto</v>
+        <v>Alessandra Maria do Nascimento Araújo</v>
       </c>
       <c r="B4" t="str">
-        <v>joao.correa@pedroleopoldo.mg.gov.br</v>
+        <v>alessandranascimentoaraujo3@gmail.com</v>
       </c>
       <c r="C4" t="str">
-        <v>Controladoria Geral do Município</v>
+        <v>Secretaria Municipal de Bem Estar</v>
       </c>
       <c r="D4" t="str">
-        <v>Estagiário</v>
+        <v>DCA 01</v>
       </c>
       <c r="E4" t="str">
-        <v>00000</v>
+        <v>36040</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -516,7 +512,7 @@
         <v>Sim</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-05-19 15:48:46</v>
+        <v>2026-05-21 09:24:21</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -524,19 +520,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jussara Batista Araújo Alves</v>
+        <v>Ana Carolina Fagundes</v>
       </c>
       <c r="B5" t="str">
-        <v>jussara.alves@pedroleopoldo.mg.gov.br</v>
+        <v>ana.fonseca@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C5" t="str">
-        <v>Controladoria Geral do Município</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D5" t="str">
-        <v>Ouvidora Municipal</v>
+        <v>Assessora</v>
       </c>
       <c r="E5" t="str">
-        <v>36054</v>
+        <v>36100</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -545,7 +541,7 @@
         <v>Sim</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-05-19 15:50:10</v>
+        <v>2026-05-20 16:46:13</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -553,19 +549,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tânia Aparecida Silva Ribeiro</v>
+        <v>Ana de Jesus</v>
       </c>
       <c r="B6" t="str">
-        <v>tania.ribeiro@pedroleopoldo.mg.gov.br</v>
+        <v>ana.jesus@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C6" t="str">
-        <v>Controladoria Geral do Município</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D6" t="str">
-        <v>DCA-3</v>
+        <v>Analista Administrativo</v>
       </c>
       <c r="E6" t="str">
-        <v>36062</v>
+        <v>0000</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -574,7 +570,7 @@
         <v>Sim</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-05-19 15:50:15</v>
+        <v>2026-05-20 09:07:06</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -582,19 +578,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Polyana Parreiras</v>
+        <v>Auricelio Alves de Souza Sobrinho</v>
       </c>
       <c r="B7" t="str">
-        <v>polyana.parreiras@pedroleopoldo.mg.gov.br</v>
+        <v>auricelio.souza@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C7" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D7" t="str">
-        <v>Assistente Adminitrativo</v>
+        <v>Secretário adjunto de gestão administrativa</v>
       </c>
       <c r="E7" t="str">
-        <v>8753</v>
+        <v>35087</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -603,7 +599,7 @@
         <v>Sim</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-05-19 15:50:55</v>
+        <v>2026-05-21 09:24:21</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -611,28 +607,28 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Leandro Macedo</v>
+        <v>Brena Diniz Costa</v>
       </c>
       <c r="B8" t="str">
-        <v>leandro.ramos.macedo@gmail.com</v>
+        <v>brena.souza@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C8" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Desenvolvimento Social</v>
       </c>
       <c r="D8" t="str">
-        <v>Coordenador Patrimônio</v>
+        <v>Psicólogo</v>
       </c>
       <c r="E8" t="str">
-        <v>36494</v>
+        <v>34891</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-05-19 16:07:16</v>
+        <v>2026-05-20 14:49:12</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -640,28 +636,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Libânia Cássia Alves</v>
+        <v>Bruno Simões Marques</v>
       </c>
       <c r="B9" t="str">
-        <v>libaniacassia@hotmail.com</v>
+        <v>brunosimoespl@hotmail.com</v>
       </c>
       <c r="C9" t="str">
-        <v>Secretaria Municipal de Governo</v>
+        <v>Chefia de Gabinete</v>
       </c>
       <c r="D9" t="str">
-        <v>Coordenadora</v>
+        <v>Social Mídia</v>
       </c>
       <c r="E9" t="str">
-        <v>0001</v>
+        <v>36872</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-05-19 17:16:51</v>
+        <v>2026-05-21 09:24:21</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -669,19 +665,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Diego Domiciano</v>
+        <v>Cassiano Henrique</v>
       </c>
       <c r="B10" t="str">
-        <v>diego.santos@pedroleopoldo.mg.gov.br</v>
+        <v>ch.unico@hotmail.com</v>
       </c>
       <c r="C10" t="str">
-        <v>Secretaria Municipal de Governo</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D10" t="str">
-        <v>DCA 4</v>
+        <v>Supervisor de Zeladoria e Manutenção</v>
       </c>
       <c r="E10" t="str">
-        <v>36843</v>
+        <v>35067</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -690,7 +686,7 @@
         <v>Sim</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-05-20 00:22:28</v>
+        <v>2026-05-20 12:20:39</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -698,19 +694,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Priscila Soares Malaquias</v>
+        <v>Diego Domiciano</v>
       </c>
       <c r="B11" t="str">
-        <v>priscila.malaquias@pedroleopoldo.mg.gov.br</v>
+        <v>diego.santos@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C11" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Governo</v>
       </c>
       <c r="D11" t="str">
-        <v>Analista Administrativo</v>
+        <v>DCA 4</v>
       </c>
       <c r="E11" t="str">
-        <v>36839</v>
+        <v>36843</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -719,7 +715,7 @@
         <v>Sim</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-05-20 08:50:59</v>
+        <v>2026-05-20 00:22:28</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -727,19 +723,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Thais Aparecida</v>
+        <v>Fabiana Cristina da Silva</v>
       </c>
       <c r="B12" t="str">
-        <v>thaisaparecidamtz@hotmail.com</v>
+        <v>fabiana.silva@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C12" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D12" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Gerente de Cargos, Carreiras e Desenvolvimento</v>
       </c>
       <c r="E12" t="str">
-        <v>36840</v>
+        <v>10013</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -748,7 +744,7 @@
         <v>Sim</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-05-20 08:54:45</v>
+        <v>2026-05-20 20:32:57</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -756,19 +752,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Renata Dias</v>
+        <v>Flaviane Rodrigues</v>
       </c>
       <c r="B13" t="str">
-        <v>renata.dias@pedroleopoldo.mg.gov.br</v>
+        <v>flavianerodrigues89@gmail.com</v>
       </c>
       <c r="C13" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Segurança Pública</v>
       </c>
       <c r="D13" t="str">
-        <v>Assistente Administrativo/dca 3</v>
+        <v>Dca 5</v>
       </c>
       <c r="E13" t="str">
-        <v>8754</v>
+        <v>35998</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -777,7 +773,7 @@
         <v>Sim</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-05-20 08:55:39</v>
+        <v>2026-05-20 19:36:47</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -785,19 +781,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Maria Estevam</v>
+        <v>Hugor Simão Oliveira Silva</v>
       </c>
       <c r="B14" t="str">
-        <v>mariainesbassouto@yahoo.com.br</v>
+        <v>hugor812010@gmail.com</v>
       </c>
       <c r="C14" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Gabinete do Prefeito</v>
       </c>
       <c r="D14" t="str">
-        <v>Gerente</v>
+        <v>Chefe de gabinete</v>
       </c>
       <c r="E14" t="str">
-        <v>8295</v>
+        <v>35056</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -806,7 +802,7 @@
         <v>Sim</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-05-20 08:59:04</v>
+        <v>2026-05-21 09:24:21</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -814,19 +810,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Patricia Pereira de Araujo Fernandes</v>
+        <v>Jessica Roberta</v>
       </c>
       <c r="B15" t="str">
-        <v>paty2582@gmail.com</v>
+        <v>jessicaroberta1726@gmail.com</v>
       </c>
       <c r="C15" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Governo</v>
       </c>
       <c r="D15" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Servidor Público</v>
       </c>
       <c r="E15" t="str">
-        <v>8305</v>
+        <v>35959</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -835,7 +831,7 @@
         <v>Sim</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-05-20 09:04:45</v>
+        <v>2026-05-20 12:08:32</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -843,19 +839,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Ana de Jesus</v>
+        <v>João Pedro Corrêa Peixoto</v>
       </c>
       <c r="B16" t="str">
-        <v>ana.jesus@pedroleopoldo.mg.gov.br</v>
+        <v>joao.correa@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C16" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Controladoria Geral do Município</v>
       </c>
       <c r="D16" t="str">
-        <v>Analista Administrativo</v>
+        <v>Estagiário</v>
       </c>
       <c r="E16" t="str">
-        <v>0000</v>
+        <v>00000</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -864,7 +860,7 @@
         <v>Sim</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-05-20 09:07:06</v>
+        <v>2026-05-19 15:48:46</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -872,28 +868,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Adriane Marques</v>
+        <v>Jussara Batista Araújo Alves</v>
       </c>
       <c r="B17" t="str">
-        <v>adrianemarquezcursos@gmail.com</v>
+        <v>jussara.alves@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C17" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Controladoria Geral do Município</v>
       </c>
       <c r="D17" t="str">
-        <v>Assesoria e Atendimento</v>
+        <v>Ouvidora Municipal</v>
       </c>
       <c r="E17" t="str">
-        <v>35078</v>
+        <v>36054</v>
       </c>
       <c r="F17" t="str">
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-05-20 09:10:05</v>
+        <v>2026-05-19 15:50:10</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -901,19 +897,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Adriana Cristiene Demétrio</v>
+        <v>Ketylin Franciny</v>
       </c>
       <c r="B18" t="str">
-        <v>adriana.demetrio@pedroleopoldo.mg.gov.br</v>
+        <v>francinyketylin@gmail.com</v>
       </c>
       <c r="C18" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Chefia de Gabinete</v>
       </c>
       <c r="D18" t="str">
-        <v>Assistente Administrativo</v>
+        <v>Coordenadora Comunicação</v>
       </c>
       <c r="E18" t="str">
-        <v>9257</v>
+        <v>35081</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -922,7 +918,7 @@
         <v>Sim</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-05-20 09:24:52</v>
+        <v>2026-05-21 09:16:11</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -930,19 +926,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessica Roberta</v>
+        <v>Leandro Macedo</v>
       </c>
       <c r="B19" t="str">
-        <v>jessicaroberta1726@gmail.com</v>
+        <v>leandro.ramos.macedo@gmail.com</v>
       </c>
       <c r="C19" t="str">
-        <v>Secretaria Municipal de Governo</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D19" t="str">
-        <v>Servidor Público</v>
+        <v>Coordenador Patrimônio</v>
       </c>
       <c r="E19" t="str">
-        <v>35959</v>
+        <v>36494</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -951,7 +947,7 @@
         <v>Sim</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-05-20 12:08:32</v>
+        <v>2026-05-19 16:07:16</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -959,19 +955,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cassiano Henrique</v>
+        <v>Libânia Cássia Alves</v>
       </c>
       <c r="B20" t="str">
-        <v>ch.unico@hotmail.com</v>
+        <v>libaniacassia@hotmail.com</v>
       </c>
       <c r="C20" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Secretaria Municipal de Governo</v>
       </c>
       <c r="D20" t="str">
-        <v>Supervisor de Zeladoria e Manutenção</v>
+        <v>Coordenadora</v>
       </c>
       <c r="E20" t="str">
-        <v>35067</v>
+        <v>0001</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -980,7 +976,7 @@
         <v>Sim</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-05-20 12:20:39</v>
+        <v>2026-05-19 17:16:51</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -988,28 +984,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Brena Diniz Costa</v>
+        <v>Makerly Aparecida Maia Toledo</v>
       </c>
       <c r="B21" t="str">
-        <v>brena.souza@pedroleopoldo.mg.gov.br</v>
+        <v>makerlymaiatoledo@gmail.com</v>
       </c>
       <c r="C21" t="str">
-        <v>Secretaria Municipal de Desenvolvimento Social</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D21" t="str">
-        <v>Psicólogo</v>
+        <v>Diretor</v>
       </c>
       <c r="E21" t="str">
-        <v>34891</v>
+        <v>3499-5</v>
       </c>
       <c r="F21" t="str">
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-05-20 14:49:12</v>
+        <v>2026-05-19 15:46:12</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1017,10 +1013,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tássia Junqueira</v>
+        <v>Maria Inês Clemente Bassouto Estevam</v>
       </c>
       <c r="B22" t="str">
-        <v>tassia.junqueira@pedroleopoldo.mg.gov.br</v>
+        <v>mariainesbassouto@yahoo.com.br</v>
       </c>
       <c r="C22" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
@@ -1029,7 +1025,7 @@
         <v>Gerente</v>
       </c>
       <c r="E22" t="str">
-        <v>34996</v>
+        <v>8295</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1038,7 +1034,7 @@
         <v>Sim</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-05-20 15:52:58</v>
+        <v>2026-05-20 08:59:04</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1046,19 +1042,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Ana Carolina Fagundes</v>
+        <v>Maria Paula Martins de Oliveira</v>
       </c>
       <c r="B23" t="str">
-        <v>ana.fonseca@pedroleopoldo.mg.gov.br</v>
+        <v>mariapaulamart66@gmail.com</v>
       </c>
       <c r="C23" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Gabinete do Vice-Prefeito</v>
       </c>
       <c r="D23" t="str">
-        <v>Assessora</v>
+        <v>Assessor de Comunicação do Vice-Prefeito</v>
       </c>
       <c r="E23" t="str">
-        <v>36100</v>
+        <v>35066</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1067,7 +1063,7 @@
         <v>Sim</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-05-20 16:46:13</v>
+        <v>2026-05-21 09:16:02</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1075,19 +1071,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Flaviane Rodrigues</v>
+        <v>Olga Arruda</v>
       </c>
       <c r="B24" t="str">
-        <v>flavianerodrigues89@gmail.com</v>
+        <v>olga_arruda@hotmail.com</v>
       </c>
       <c r="C24" t="str">
-        <v>Secretaria Municipal de Segurança Pública</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D24" t="str">
-        <v>Dca 5</v>
+        <v>Supervisora</v>
       </c>
       <c r="E24" t="str">
-        <v>35998</v>
+        <v>33291</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1096,7 +1092,7 @@
         <v>Sim</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-05-20 19:36:47</v>
+        <v>2026-05-20 19:55:54</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1104,19 +1100,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olga Arruda</v>
+        <v>Patricia Pereira de Araujo Fernandes</v>
       </c>
       <c r="B25" t="str">
-        <v>olga_arruda@hotmail.com</v>
+        <v>paty2582@gmail.com</v>
       </c>
       <c r="C25" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D25" t="str">
-        <v>Supervisora</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E25" t="str">
-        <v>33291</v>
+        <v>8305</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1125,7 +1121,7 @@
         <v>Sim</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-05-20 19:55:54</v>
+        <v>2026-05-20 09:04:45</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1133,19 +1129,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Fabiana Cristina da Silva</v>
+        <v>Polyana Parreiras</v>
       </c>
       <c r="B26" t="str">
-        <v>fabiana.silva@pedroleopoldo.mg.gov.br</v>
+        <v>polyana.parreiras@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C26" t="str">
         <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D26" t="str">
-        <v>Gerente de Cargos, Carreiras e Desenvolvimento</v>
+        <v>Assistente Adminitrativo</v>
       </c>
       <c r="E26" t="str">
-        <v>10013</v>
+        <v>8753</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1154,7 +1150,7 @@
         <v>Sim</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-05-20 20:32:57</v>
+        <v>2026-05-19 15:50:55</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1162,19 +1158,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Maria Paula Martins de Oliveira</v>
+        <v>Priscila Soares Malaquias</v>
       </c>
       <c r="B27" t="str">
-        <v>mariapaulamart66@gmail.com</v>
+        <v>priscila.malaquias@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C27" t="str">
-        <v>Gabinete do Vice-Prefeito</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D27" t="str">
-        <v>Assessor de Comunicação do Vice-Prefeito</v>
+        <v>Analista Administrativo</v>
       </c>
       <c r="E27" t="str">
-        <v>35066</v>
+        <v>36839</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1183,7 +1179,7 @@
         <v>Sim</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-05-21 09:16:02</v>
+        <v>2026-05-20 08:50:59</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1191,19 +1187,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ketylin Franciny</v>
+        <v>Renata Dias</v>
       </c>
       <c r="B28" t="str">
-        <v>francinyketylin@gmail.com</v>
+        <v>renata.dias@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C28" t="str">
-        <v>Chefia de Gabinete</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D28" t="str">
-        <v>Coordenadora Comunicação</v>
+        <v>Assistente Administrativo/dca 3</v>
       </c>
       <c r="E28" t="str">
-        <v>35081</v>
+        <v>8754</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1212,7 +1208,7 @@
         <v>Sim</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-05-21 09:16:11</v>
+        <v>2026-05-20 08:55:39</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1220,28 +1216,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Simões Marques</v>
+        <v>Renata dos Santos Nestor</v>
       </c>
       <c r="B29" t="str">
-        <v>brunosimoespl@hotmail.com</v>
+        <v>renata.nestor@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C29" t="str">
-        <v>Chefia de Gabinete</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D29" t="str">
-        <v>Social Mídia</v>
+        <v>DCA 3</v>
       </c>
       <c r="E29" t="str">
-        <v>36872</v>
+        <v>08307</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-05-21 09:24:21</v>
+        <v>2026-05-19 15:47:55</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1249,19 +1245,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Alessandra Maria do Nascimento Araújo</v>
+        <v>Suelen Lorraine Sodré Pimentel</v>
       </c>
       <c r="B30" t="str">
-        <v>alessandranascimentoaraujo3@gmail.com</v>
+        <v>suelen.pimentel@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C30" t="str">
-        <v>Secretaria Municipal de Bem Estar</v>
+        <v>Secretaria Municipal de Obras</v>
       </c>
       <c r="D30" t="str">
-        <v>DCA 01</v>
+        <v>DCA 05</v>
       </c>
       <c r="E30" t="str">
-        <v>36040</v>
+        <v>36061</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1278,19 +1274,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Auricelio Alves de Souza Sobrinho</v>
+        <v>Tânia Aparecida Silva Ribeiro</v>
       </c>
       <c r="B31" t="str">
-        <v>auricelio.souza@pedroleopoldo.mg.gov.br</v>
+        <v>tania.ribeiro@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C31" t="str">
-        <v>Secretaria Municipal de Gestão e Finanças</v>
+        <v>Controladoria Geral do Município</v>
       </c>
       <c r="D31" t="str">
-        <v>Secretário adjunto de gestão administrativa</v>
+        <v>DCA-3</v>
       </c>
       <c r="E31" t="str">
-        <v>35087</v>
+        <v>36062</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -1299,7 +1295,7 @@
         <v>Sim</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-05-21 09:24:21</v>
+        <v>2026-05-19 15:50:15</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1307,19 +1303,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Hugor Simão Oliveira Silva</v>
+        <v>Tássia Junqueira</v>
       </c>
       <c r="B32" t="str">
-        <v>hugor812010@gmail.com</v>
+        <v>tassia.junqueira@pedroleopoldo.mg.gov.br</v>
       </c>
       <c r="C32" t="str">
-        <v>Gabinete do Prefeito</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D32" t="str">
-        <v>Chefe de gabinete</v>
+        <v>Gerente</v>
       </c>
       <c r="E32" t="str">
-        <v>35056</v>
+        <v>34996</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1328,7 +1324,7 @@
         <v>Sim</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-05-21 09:24:21</v>
+        <v>2026-05-20 15:52:58</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1336,19 +1332,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Suelen Lorraine Sodré Pimentel</v>
+        <v>Thais Aparecida</v>
       </c>
       <c r="B33" t="str">
-        <v>suelen.pimentel@pedroleopoldo.mg.gov.br</v>
+        <v>thaisaparecidamtz@hotmail.com</v>
       </c>
       <c r="C33" t="str">
-        <v>Secretaria Municipal de Obras</v>
+        <v>Secretaria Municipal de Gestão e Finanças</v>
       </c>
       <c r="D33" t="str">
-        <v>DCA 05</v>
+        <v>Assistente Administrativo</v>
       </c>
       <c r="E33" t="str">
-        <v>36061</v>
+        <v>36840</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1357,7 +1353,7 @@
         <v>Sim</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-05-21 09:24:21</v>
+        <v>2026-05-20 08:54:45</v>
       </c>
       <c r="I33" t="str">
         <v/>
